--- a/CoreEngine/GameData/Test/CSV/TestTable.xlsx
+++ b/CoreEngine/GameData/Test/CSV/TestTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23EF8A97-7829-49AB-B94C-F2C764DDD5C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E00867D-8C89-43F5-A128-3D3585C8F52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B21" s="2">
         <v>32.5</v>

--- a/CoreEngine/GameData/Test/CSV/TestTable.xlsx
+++ b/CoreEngine/GameData/Test/CSV/TestTable.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\CoreFramework Develop\Assets\_WorkSpace\CoreFramework\CoreEngine\GameData\Test\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E00867D-8C89-43F5-A128-3D3585C8F52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A3A6A8-832F-4F67-93C6-065A35DE306B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2">
         <v>32.5</v>
